--- a/human_validation/judge/kor/judge_D006_S003_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S003_P002__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,271 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 오게 된 건 식사가 정말 들쭉날쭉해져서예요. 어떤 주는 저녁을 거의 안 먹다시피 하고, 또 어떤 날 밤에는 다들 자고 난 뒤에 부엌에서 크래커랑 단 것들을 먹고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 밤늦게 그렇게 드실 때, 멈추거나 양을 조절할 수 없다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 어떤 밤은 그래요. 뭔가 조금 먹으려고 갔다가 계속 크래커랑 단 것들을 먹게 돼요. 근데 또 어떤 주는 저녁 먹는 것 자체가 거의 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 신경성 폭식증 (D022); 폭식장애 (D023) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 밤에 많이 드신 후에, 먹은 걸 만회하려고 일부러 토하거나 완하제를 먹거나 격하게 운동하는 것 같은 행동을 하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아니요, 그런 건 딱히 안 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 폭식장애 (D023) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 식사 변화 말고, 요즘 기분은 어떠셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 한동안 계속 좀 가라앉아 있었어요. 집이 그냥 회색빛에 무겁게 느껴지고, 부엌 식탁에 앉아서 공허함을 느껴요, 딱히 그날 안 좋은 일이 있었던 것도 아닌데요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 폭식장애 (D023) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 평소에 즐기시던 활동들에 흥미나 즐거움을 잃으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 예전에 기대하던 것들—독서 모임, 요리, 갤러리 가기, 심지어 장미밭 가꾸는 것까지—요즘은 그냥 해야 할 일처럼 느껴져요. 계속 미루게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이렇게 기분이 가라앉고 흥미를 잃은 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 이제 한 일곱 달쯤 쌓인 것 같아요—회색빛에 죄책감 드는 시기들이요, 그냥 아무것에도 신경이 안 쓰이는 거요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 예전에도 이렇게 가라앉고 흥미를 잃는 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네, 예전에도 이런 시기가 있었어요—모든 게 회색빛에 무겁게 느껴지고, 딱히 끔찍한 일이 없었는데도 그냥 앉아서 공허함을 느끼는 거요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 이런 식사 변화가 기분이 완전히 괜찮을 때도 일어나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 아니요, 기분이 가라앉을 때랑 연관돼 있는 것 같아요. 어떤 주는 저녁을 거의 안 먹고, 또 어떤 날 밤에는 다들 자고 난 뒤에 부엌에서 크래커랑 단 것들을 먹게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 유난히 에너지가 넘치고 흥분되거나 세상을 다 가진 것 같은 느낌이 들면서 잠을 거의 안 자도 되는 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네. 어떤 때는 서너 시간만 자고도 정말 충전된 느낌으로 깨어나요, 해가 뜨기도 전에 블로그 글을 쓰거나 프로젝트를 계획할 준비가 된 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 그렇게 에너지가 넘치고 잠을 덜 자도 되는 시기가 있을 때, 보통 며칠이나 연속으로 이어지나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 며칠이나 연속되는지는 정확히 잘 모르겠어요. 그렇게 자세히 기록해 두지는 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 그렇게 유난히 에너지가 넘쳤던 시기에, 생각이 빠르게 질주하는 것처럼 느껴졌나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네. 생각이 정말 빠르게 흘러가요, 마치 한 아이디어가 바로 다음 걸로 넘어가는 것처럼요—장미, 돈, 색깔, 메시지, 수업들—그리고 그걸 충분히 늦추지 못해서 제가 뭘 말하려는 건지 설명을 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 그렇게 에너지가 넘치는 시기에, 업무나 인간관계, 일상적인 책임에 눈에 띄는 문제가 생긴 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네. 퍼실리테이터 교육이랑 개인 블로그 일이 뒤처졌어요, 프로젝트를 너무 많이 벌여놓고 나면 생각을 정리하거나 명확하게 설명하기가 힘들어지거든요. 그게 집에서도 긴장을 일으켰고, 그래서 남편이랑 평소의 일상을 유지하기가 더 힘들어졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현정동장애 (양극형) (D006)
 인구통계: 성별 여성 / 나이 46 / 직업상태 no occupation / 최종학력 대학 재학
@@ -575,347 +831,57 @@
 증상 지속 기간: 2 years and 5 months
 추가 요건: psychotic_symptoms and manic_episode occur concurrently, manic_episode is present for the majority of the total duration of the active and residual portions of the illness, delusions_and_hallucinations occur for 2 or more weeks in the absence of a major mood episode
 주호소 증상 코드: S026
-배경 서술: 니콜의 병이 뚜렷해진 것은 집안 지출, 그녀의 희귀 안료 구입, 그리고 정원 사진, 시, 미술치료 워크숍 기획에 쏟는 시간을 두고 배우자와의 말다툼이 급격히 늘어난 시기였다. 2년 5개월에 걸쳐, 그녀의 창작 에너지는 때때로 지나치게 확장되고 과도하게 벌여놓는 방향으로 흘렀다가, 이어서 갤러리 관람, 독서 모임, 요리, 장미 정원 가꾸기에 대한 즐거움을 완전히 잃어버리는 긴 시기가 뒤따랐고, 그녀의 식사 패턴과 죄책감은 가족이 무시하기 힘든 수준이 되었다. 고정된 믿음, 생생한 지각 경험, 자신의 프로젝트에 대해 점점 따라가기 힘든 설명들이 기분이 뚜렷하게 고양되거나 가라앉지 않은 시기에도 그녀의 퍼실리테이터 교육과 개인 블로그 작업을 흐트러뜨리기 시작했다. 그녀는 여전히 어느 정도 병식을 유지하고 있었고 결혼 생활과 자원봉사 계획을 지키고 싶어 했기 때문에, 스스로 1차 진료 의사에게 연락했고 외래 정신과 의뢰를 받아들였다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 오게 된 건 식사가 정말 들쭉날쭉해져서예요. 어떤 주는 저녁을 거의 안 먹다시피 하고, 또 어떤 날 밤에는 다들 자고 난 뒤에 부엌에서 크래커랑 단 것들을 먹고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 밤늦게 그렇게 드실 때, 멈추거나 양을 조절할 수 없다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 어떤 밤은 그래요. 뭔가 조금 먹으려고 갔다가 계속 크래커랑 단 것들을 먹게 돼요. 근데 또 어떤 주는 저녁 먹는 것 자체가 거의 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 신경성 폭식증 (D022); 폭식장애 (D023) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 밤에 많이 드신 후에, 먹은 걸 만회하려고 일부러 토하거나 완하제를 먹거나 격하게 운동하는 것 같은 행동을 하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아니요, 그런 건 딱히 안 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 폭식장애 (D023) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 식사 변화 말고, 요즘 기분은 어떠셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 한동안 계속 좀 가라앉아 있었어요. 집이 그냥 회색빛에 무겁게 느껴지고, 부엌 식탁에 앉아서 공허함을 느껴요, 딱히 그날 안 좋은 일이 있었던 것도 아닌데요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 폭식장애 (D023) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 평소에 즐기시던 활동들에 흥미나 즐거움을 잃으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 예전에 기대하던 것들—독서 모임, 요리, 갤러리 가기, 심지어 장미밭 가꾸는 것까지—요즘은 그냥 해야 할 일처럼 느껴져요. 계속 미루게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이렇게 기분이 가라앉고 흥미를 잃은 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 이제 한 일곱 달쯤 쌓인 것 같아요—회색빛에 죄책감 드는 시기들이요, 그냥 아무것에도 신경이 안 쓰이는 거요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 예전에도 이렇게 가라앉고 흥미를 잃는 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네, 예전에도 이런 시기가 있었어요—모든 게 회색빛에 무겁게 느껴지고, 딱히 끔찍한 일이 없었는데도 그냥 앉아서 공허함을 느끼는 거요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 이런 식사 변화가 기분이 완전히 괜찮을 때도 일어나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 아니요, 기분이 가라앉을 때랑 연관돼 있는 것 같아요. 어떤 주는 저녁을 거의 안 먹고, 또 어떤 날 밤에는 다들 자고 난 뒤에 부엌에서 크래커랑 단 것들을 먹게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 유난히 에너지가 넘치고 흥분되거나 세상을 다 가진 것 같은 느낌이 들면서 잠을 거의 안 자도 되는 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네. 어떤 때는 서너 시간만 자고도 정말 충전된 느낌으로 깨어나요, 해가 뜨기도 전에 블로그 글을 쓰거나 프로젝트를 계획할 준비가 된 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 그렇게 에너지가 넘치고 잠을 덜 자도 되는 시기가 있을 때, 보통 며칠이나 연속으로 이어지나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 며칠이나 연속되는지는 정확히 잘 모르겠어요. 그렇게 자세히 기록해 두지는 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 그렇게 유난히 에너지가 넘쳤던 시기에, 생각이 빠르게 질주하는 것처럼 느껴졌나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네. 생각이 정말 빠르게 흘러가요, 마치 한 아이디어가 바로 다음 걸로 넘어가는 것처럼요—장미, 돈, 색깔, 메시지, 수업들—그리고 그걸 충분히 늦추지 못해서 제가 뭘 말하려는 건지 설명을 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 그렇게 에너지가 넘치는 시기에, 업무나 인간관계, 일상적인 책임에 눈에 띄는 문제가 생긴 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네. 퍼실리테이터 교육이랑 개인 블로그 일이 뒤처졌어요, 프로젝트를 너무 많이 벌여놓고 나면 생각을 정리하거나 명확하게 설명하기가 힘들어지거든요. 그게 집에서도 긴장을 일으켰고, 그래서 남편이랑 평소의 일상을 유지하기가 더 힘들어졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
+배경 서술: 니콜의 병이 뚜렷해진 것은 집안 지출, 그녀의 희귀 안료 구입, 그리고 정원 사진, 시, 미술치료 워크숍 기획에 쏟는 시간을 두고 배우자와의 말다툼이 급격히 늘어난 시기였다. 2년 5개월에 걸쳐, 그녀의 창작 에너지는 때때로 지나치게 확장되고 과도하게 벌여놓는 방향으로 흘렀다가, 이어서 갤러리 관람, 독서 모임, 요리, 장미 정원 가꾸기에 대한 즐거움을 완전히 잃어버리는 긴 시기가 뒤따랐고, 그녀의 식사 패턴과 죄책감은 가족이 무시하기 힘든 수준이 되었다. 고정된 믿음, 생생한 지각 경험, 자신의 프로젝트에 대해 점점 따라가기 힘든 설명들이 기분이 뚜렷하게 고양되거나 가라앉지 않은 시기에도 그녀의 퍼실리테이터 교육과 개인 블로그 작업을 흐트러뜨리기 시작했다. 그녀는 여전히 어느 정도 병식을 유지하고 있었고 결혼 생활과 자원봉사 계획을 지키고 싶어 했기 때문에, 스스로 1차 진료 의사에게 연락했고 외래 정신과 의뢰를 받아들였다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S021 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S036 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - S038 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.
+  - S039 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.</t>
+        </is>
+      </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 폭식장애 (D023) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: None (None, ICD: F31)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.; 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.; 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.; 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
-  확인된 근거: 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
-  누락: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
+          <t>의사의 최종 진단: None (None, ICD: F31)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 없음
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
+확인된 근거:
+  - 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.
+  - 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A52:B52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D006_S003_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S003_P002__gemini-3.8-flash_kor.xlsx
@@ -817,6 +817,11 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -877,11 +882,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A52:B52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D006_S003_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S003_P002__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1414</v>
+        <v>0.1769</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1484</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3636</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
